--- a/AAAGameData/DataTables/Core/ArrowLanguagesTable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowLanguagesTable.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\smash\AAAGameData\DataTables\Core\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
@@ -123,6 +128,21 @@
   </si>
   <si>
     <t>PortuguesePortugal</t>
+  </si>
+  <si>
+    <t>Indonesian</t>
+  </si>
+  <si>
+    <t>Filipino</t>
+  </si>
+  <si>
+    <t>Turkish</t>
+  </si>
+  <si>
+    <t>Thai</t>
+  </si>
+  <si>
+    <t>Hindi</t>
   </si>
 </sst>
 </file>
@@ -758,7 +778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -767,6 +787,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1086,7 +1107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="23.2857142857143" customWidth="1"/>
@@ -1263,6 +1284,76 @@
         <v>21</v>
       </c>
     </row>
+    <row r="12" spans="1:7">
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D3:AA3">
